--- a/REopt Julia Package Scripts/results/min_payback_results.xlsx
+++ b/REopt Julia Package Scripts/results/min_payback_results.xlsx
@@ -8,24 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbernal\Documents\GitHub\REopt-Analysis-Scripts\REopt Julia Package Scripts\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47575371-73C6-4A7D-B1E8-5F6B4F7E291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A40A5E9-8751-4AF2-A617-2F4D0C4DFD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="Result_1" sheetId="2" r:id="rId1"/>
+    <sheet name="Result_0" sheetId="4" r:id="rId1"/>
+    <sheet name="Result_1" sheetId="2" r:id="rId2"/>
+    <sheet name="Result_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Result_3" sheetId="5" r:id="rId4"/>
+    <sheet name="Result_4" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="109">
   <si>
     <t>threshold_payback</t>
   </si>
@@ -121,18 +136,250 @@
   </si>
   <si>
     <t>IRR</t>
+  </si>
+  <si>
+    <t>threshold_payback</t>
+  </si>
+  <si>
+    <t>payback_years</t>
+  </si>
+  <si>
+    <t>npv</t>
+  </si>
+  <si>
+    <t>lcc</t>
+  </si>
+  <si>
+    <t>lcc_BAU</t>
+  </si>
+  <si>
+    <t>PV_size</t>
+  </si>
+  <si>
+    <t>PV_all_year1_production</t>
+  </si>
+  <si>
+    <t>PV_all_annual_energy_production_avg</t>
+  </si>
+  <si>
+    <t>PV_all_energy_lcoe</t>
+  </si>
+  <si>
+    <t>PV_all_serving_load</t>
+  </si>
+  <si>
+    <t>PV_all_energy_exported</t>
+  </si>
+  <si>
+    <t>PV_all_energy_curtailed</t>
+  </si>
+  <si>
+    <t>PV_all_energy_to_Battery_year1</t>
+  </si>
+  <si>
+    <t>Battery_size_kw</t>
+  </si>
+  <si>
+    <t>Battery_size_kwh</t>
+  </si>
+  <si>
+    <t>Grid_Electricity_Supplied_kWh_annual</t>
+  </si>
+  <si>
+    <t>Grid_Electricity_Supplied_kWh_annual_bau</t>
+  </si>
+  <si>
+    <t>LifeCycle_Emission_Reduction_Fraction</t>
+  </si>
+  <si>
+    <t>LifeCycle_capex_costs_for_generation_techs</t>
+  </si>
+  <si>
+    <t>LifeCycle_capex_costs_for_battery</t>
+  </si>
+  <si>
+    <t>Initial_upfront_capex_wo_incentives</t>
+  </si>
+  <si>
+    <t>Initial_upfront_capex_w_incentives</t>
+  </si>
+  <si>
+    <t>Initial_upfront_battery_capex</t>
+  </si>
+  <si>
+    <t>Present_cost_of_replacement_battery_after_tax</t>
+  </si>
+  <si>
+    <t>Year1_lifecycle_costs_om_before_tax</t>
+  </si>
+  <si>
+    <t>Yr1_energy_cost_after_tax</t>
+  </si>
+  <si>
+    <t>Yr1_demand_cost_after_tax</t>
+  </si>
+  <si>
+    <t>Yr1_total_energy_bill_before_tax</t>
+  </si>
+  <si>
+    <t>Year1_elec_bill_before_tax_bau</t>
+  </si>
+  <si>
+    <t>Yr1_export_benefit_before_tax</t>
+  </si>
+  <si>
+    <t>Yr1_total_operating_cost_before_tax</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>PV only - 5 years payback</t>
+  </si>
+  <si>
+    <t>PV only - 10 years payback</t>
+  </si>
+  <si>
+    <t>PV only - 15 years payback</t>
+  </si>
+  <si>
+    <t>PV only - 20 years payback</t>
+  </si>
+  <si>
+    <t>PV only - 25 years payback</t>
+  </si>
+  <si>
+    <t>PV only maxed at baseload - 5 years payback</t>
+  </si>
+  <si>
+    <t>PV only maxed at baseload - 10 years payback</t>
+  </si>
+  <si>
+    <t>PV only maxed at baseload - 15 years payback</t>
+  </si>
+  <si>
+    <t>PV only maxed at baseload - 20 years payback</t>
+  </si>
+  <si>
+    <t>PV only maxed at baseload - 25 years payback</t>
+  </si>
+  <si>
+    <t>threshold_payback</t>
+  </si>
+  <si>
+    <t>payback_years</t>
+  </si>
+  <si>
+    <t>npv</t>
+  </si>
+  <si>
+    <t>lcc</t>
+  </si>
+  <si>
+    <t>lcc_BAU</t>
+  </si>
+  <si>
+    <t>PV_size</t>
+  </si>
+  <si>
+    <t>PV_all_year1_production</t>
+  </si>
+  <si>
+    <t>PV_all_annual_energy_production_avg</t>
+  </si>
+  <si>
+    <t>PV_all_energy_lcoe</t>
+  </si>
+  <si>
+    <t>PV_all_serving_load</t>
+  </si>
+  <si>
+    <t>PV_all_energy_exported</t>
+  </si>
+  <si>
+    <t>PV_all_energy_curtailed</t>
+  </si>
+  <si>
+    <t>PV_all_energy_to_Battery_year1</t>
+  </si>
+  <si>
+    <t>Battery_size_kw</t>
+  </si>
+  <si>
+    <t>Battery_size_kwh</t>
+  </si>
+  <si>
+    <t>Grid_Electricity_Supplied_kWh_annual</t>
+  </si>
+  <si>
+    <t>Grid_Electricity_Supplied_kWh_annual_bau</t>
+  </si>
+  <si>
+    <t>LifeCycle_Emission_Reduction_Fraction</t>
+  </si>
+  <si>
+    <t>LifeCycle_capex_costs_for_generation_techs</t>
+  </si>
+  <si>
+    <t>LifeCycle_capex_costs_for_battery</t>
+  </si>
+  <si>
+    <t>Initial_upfront_capex_wo_incentives</t>
+  </si>
+  <si>
+    <t>Initial_upfront_capex_w_incentives</t>
+  </si>
+  <si>
+    <t>Initial_upfront_battery_capex</t>
+  </si>
+  <si>
+    <t>Present_cost_of_replacement_battery_after_tax</t>
+  </si>
+  <si>
+    <t>Year1_lifecycle_costs_om_before_tax</t>
+  </si>
+  <si>
+    <t>Yr1_energy_cost_after_tax</t>
+  </si>
+  <si>
+    <t>Yr1_demand_cost_after_tax</t>
+  </si>
+  <si>
+    <t>Yr1_total_energy_bill_before_tax</t>
+  </si>
+  <si>
+    <t>Year1_elec_bill_before_tax_bau</t>
+  </si>
+  <si>
+    <t>Yr1_export_benefit_before_tax</t>
+  </si>
+  <si>
+    <t>Yr1_total_operating_cost_before_tax</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Getting base</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -158,12 +405,21 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -172,27 +428,47 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -508,1091 +784,3715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEB6BD4-7B66-4D49-8EDC-D32F3AE5B38D}">
-  <dimension ref="A1:AF11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB683ABC-5B6F-4AB0-8F3E-105C4146221A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E789FCE6-F619-40B3-BCC6-22AAC0287BCF}">
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="5"/>
-    <col min="7" max="8" width="12.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="9"/>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="5"/>
+    <col min="8" max="9" width="12.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="9"/>
+    <col min="11" max="11" width="11" style="16"/>
+    <col min="13" max="13" width="11" style="7"/>
+    <col min="22" max="24" width="13.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="12.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.125" style="3" bestFit="1" customWidth="1"/>
   </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>6215044.21</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>8.6E-3</v>
+      </c>
+      <c r="H2" s="7">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7">
+        <v>11</v>
+      </c>
+      <c r="J2" s="9">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K2" s="16">
+        <v>2.8812500000000005</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>1825056</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>9.24</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3">
+        <v>12.87</v>
+      </c>
+      <c r="W2" s="3">
+        <v>9.24</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0.1545</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>219006.71</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>200353.85</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>419360.56</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>419360.71</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5657835.5800000001</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>496.89440000000002</v>
+      </c>
+      <c r="H3" s="7">
+        <v>703378</v>
+      </c>
+      <c r="I3" s="7">
+        <v>670227</v>
+      </c>
+      <c r="J3" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K3" s="16">
+        <v>142695.122</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>24861.667750000001</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1254287</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>534872.34</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
+        <v>745341.54</v>
+      </c>
+      <c r="W3" s="3">
+        <v>534872.34</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>8944.0985000000001</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>150514.44</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>185370.56</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>335885</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>344829.1</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5878217.6900000004</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>885.46529999999996</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1253420</v>
+      </c>
+      <c r="I4" s="7">
+        <v>1194344</v>
+      </c>
+      <c r="J4" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K4" s="16">
+        <v>178864.81475000002</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>119721.23849999999</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1109608</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>953142.08</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
+        <v>1328198.01</v>
+      </c>
+      <c r="W4" s="3">
+        <v>953142.08</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>15938.376099999999</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>133152.98000000001</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>181725.32</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>314878.3</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>330816.68</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6202988.6299999999</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1218.0920000000001</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1724269</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1643002</v>
+      </c>
+      <c r="J5" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K5" s="16">
+        <v>192439.98800000001</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>218310.4535</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1055308</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>1311191.6000000001</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <v>1827137.97</v>
+      </c>
+      <c r="W5" s="3">
+        <v>1311191.6000000001</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>21925.655599999998</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>126636.9</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>179443.74</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>306080.64000000001</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>328006.3</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="10">
+        <v>25</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>6537818.3799999999</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>1519.6361999999999</v>
+      </c>
+      <c r="H6" s="13">
+        <v>2151120</v>
+      </c>
+      <c r="I6" s="13">
+        <v>2049735</v>
+      </c>
+      <c r="J6" s="14">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K6" s="17">
+        <v>200376.00024999998</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>312057.5895</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>1023563</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0</v>
+      </c>
+      <c r="S6" s="10">
+        <v>0</v>
+      </c>
+      <c r="T6" s="10">
+        <v>1635783.1</v>
+      </c>
+      <c r="U6" s="10">
+        <v>0</v>
+      </c>
+      <c r="V6" s="11">
+        <v>2279454.36</v>
+      </c>
+      <c r="W6" s="11">
+        <v>1635783.1</v>
+      </c>
+      <c r="X6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="11">
+        <v>27353.452399999998</v>
+      </c>
+      <c r="AA6" s="11">
+        <v>122827.61</v>
+      </c>
+      <c r="AB6" s="11">
+        <v>178003.95</v>
+      </c>
+      <c r="AC6" s="11">
+        <v>300831.56</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="11">
+        <v>328185.01</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6215044.21</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>8.6E-3</v>
+      </c>
+      <c r="H7" s="7">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7">
+        <v>11</v>
+      </c>
+      <c r="J7" s="9">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K7" s="16">
+        <v>2.8812500000000005</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1825056</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>9.24</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>12.87</v>
+      </c>
+      <c r="W7" s="3">
+        <v>9.24</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0.1545</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>219006.71</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>200353.85</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>419360.56</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>419360.71</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5657835.5800000001</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>496.89440000000002</v>
+      </c>
+      <c r="H8" s="7">
+        <v>703378</v>
+      </c>
+      <c r="I8" s="7">
+        <v>670227</v>
+      </c>
+      <c r="J8" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K8" s="16">
+        <v>142695.122</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>24861.667750000001</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1254287</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>534872.34</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>745341.54</v>
+      </c>
+      <c r="W8" s="3">
+        <v>534872.34</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>8944.0985000000001</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>150514.44</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>185370.56</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>335885</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>344829.1</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5331130.97</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1106.5083999999999</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1566317</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1492494</v>
+      </c>
+      <c r="J9" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K9" s="16">
+        <v>184991.43549999999</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>23595.942999999999</v>
+      </c>
+      <c r="N9">
+        <v>164536.16425000003</v>
+      </c>
+      <c r="O9">
+        <v>392.63</v>
+      </c>
+      <c r="P9">
+        <v>5392.67</v>
+      </c>
+      <c r="Q9">
+        <v>492931</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1191079.6100000001</v>
+      </c>
+      <c r="U9">
+        <v>1411217.21</v>
+      </c>
+      <c r="V9" s="3">
+        <v>3626285.51</v>
+      </c>
+      <c r="W9" s="3">
+        <v>2602296.8199999998</v>
+      </c>
+      <c r="X9" s="3">
+        <v>1966526.35</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>69080.224100000007</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>59151.72</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>49378.97</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>108530.69</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>177610.91</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6237320.7599999998</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1214.8742</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1719714</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1638661</v>
+      </c>
+      <c r="J10" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K10" s="16">
+        <v>187808.23175000001</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>32937.380499999999</v>
+      </c>
+      <c r="N10">
+        <v>188919.74724999999</v>
+      </c>
+      <c r="O10">
+        <v>448.52</v>
+      </c>
+      <c r="P10">
+        <v>9128.5300000000007</v>
+      </c>
+      <c r="Q10">
+        <v>392897</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1307727.8500000001</v>
+      </c>
+      <c r="U10">
+        <v>2128323</v>
+      </c>
+      <c r="V10" s="3">
+        <v>4788116.8499999996</v>
+      </c>
+      <c r="W10" s="3">
+        <v>3436050.84</v>
+      </c>
+      <c r="X10" s="3">
+        <v>2965800.45</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>96012.875</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>47147.65</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>36796.92</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>83944.57</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>179957.44</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>7105338.29</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1305.7005999999999</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1848283</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1761171</v>
+      </c>
+      <c r="J11" s="9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K11" s="16">
+        <v>190509.74275</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>45374.025499999996</v>
+      </c>
+      <c r="N11">
+        <v>204409.00625000001</v>
+      </c>
+      <c r="O11">
+        <v>499.53</v>
+      </c>
+      <c r="P11">
+        <v>12375.06</v>
+      </c>
+      <c r="Q11">
+        <v>325911</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1405496.23</v>
+      </c>
+      <c r="U11">
+        <v>2753184.73</v>
+      </c>
+      <c r="V11" s="3">
+        <v>5795097.6699999999</v>
+      </c>
+      <c r="W11" s="3">
+        <v>4158680.96</v>
+      </c>
+      <c r="X11" s="3">
+        <v>3836550.22</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>119416.2797</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>39109.31</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>29033.79</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>68143.100000000006</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>187559.38</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A92CCE-0691-4DD5-B06E-51F7D340789A}">
+  <dimension ref="A1:AG11"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="7"/>
+    <col min="13" max="13" width="10.625" style="7"/>
+    <col min="17" max="17" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.875" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>6215044.21</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>8.6E-3</v>
+      </c>
+      <c r="H2" s="7">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7">
+        <v>11</v>
+      </c>
+      <c r="J2">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K2" s="7">
+        <v>2.8812500000000005</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>1825056</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>9.24</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>12.87</v>
+      </c>
+      <c r="W2">
+        <v>9.24</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.1545</v>
+      </c>
+      <c r="AA2">
+        <v>219006.71</v>
+      </c>
+      <c r="AB2">
+        <v>200353.85</v>
+      </c>
+      <c r="AC2">
+        <v>419360.56</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>419360.71</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5928617.6699999999</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>156.6326</v>
+      </c>
+      <c r="H3" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I3" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J3">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K3" s="7">
+        <v>52382.643750000003</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>435.13124999999997</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>1615537</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>168604.14</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>234948.9</v>
+      </c>
+      <c r="W3">
+        <v>168604.14</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>2819.3868000000002</v>
+      </c>
+      <c r="AA3">
+        <v>193864.43</v>
+      </c>
+      <c r="AB3">
+        <v>191708.24</v>
+      </c>
+      <c r="AC3">
+        <v>385572.67</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>388392.06</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5928617.6699999999</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>156.6326</v>
+      </c>
+      <c r="H4" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I4" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J4">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K4" s="7">
+        <v>52382.643750000003</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>435.13124999999997</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1615537</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>168604.14</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>234948.9</v>
+      </c>
+      <c r="W4">
+        <v>168604.14</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>2819.3868000000002</v>
+      </c>
+      <c r="AA4">
+        <v>193864.43</v>
+      </c>
+      <c r="AB4">
+        <v>191708.24</v>
+      </c>
+      <c r="AC4">
+        <v>385572.67</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>388392.06</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5928617.6699999999</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>156.6326</v>
+      </c>
+      <c r="H5" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I5" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J5">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K5" s="7">
+        <v>52382.643750000003</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>435.13124999999997</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1615537</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>168604.14</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>234948.9</v>
+      </c>
+      <c r="W5">
+        <v>168604.14</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>2819.3868000000002</v>
+      </c>
+      <c r="AA5">
+        <v>193864.43</v>
+      </c>
+      <c r="AB5">
+        <v>191708.24</v>
+      </c>
+      <c r="AC5">
+        <v>385572.67</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>388392.06</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="10">
+        <v>25</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>5928617.6699999999</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>156.6326</v>
+      </c>
+      <c r="H6" s="13">
+        <v>221721</v>
+      </c>
+      <c r="I6" s="13">
+        <v>211271</v>
+      </c>
+      <c r="J6" s="10">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K6" s="13">
+        <v>52382.643750000003</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>435.13124999999997</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>1615537</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0</v>
+      </c>
+      <c r="S6" s="10">
+        <v>0</v>
+      </c>
+      <c r="T6" s="10">
+        <v>168604.14</v>
+      </c>
+      <c r="U6" s="10">
+        <v>0</v>
+      </c>
+      <c r="V6" s="10">
+        <v>234948.9</v>
+      </c>
+      <c r="W6" s="10">
+        <v>168604.14</v>
+      </c>
+      <c r="X6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>2819.3868000000002</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>193864.43</v>
+      </c>
+      <c r="AB6" s="10">
+        <v>191708.24</v>
+      </c>
+      <c r="AC6" s="10">
+        <v>385572.67</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="11">
+        <v>388392.06</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6215044.21</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>8.6E-3</v>
+      </c>
+      <c r="H7" s="7">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="K7" s="7">
+        <v>2.8812500000000005</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1825056</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>9.24</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>12.87</v>
+      </c>
+      <c r="W7">
+        <v>9.24</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0.1545</v>
+      </c>
+      <c r="AA7">
+        <v>219006.71</v>
+      </c>
+      <c r="AB7">
+        <v>200353.85</v>
+      </c>
+      <c r="AC7">
+        <v>419360.56</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>419360.71</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5995789.9100000001</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>156.6326</v>
+      </c>
+      <c r="H8" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I8" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J8">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>52382.643750000003</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>435.13124999999997</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>61.79</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1615537</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>168604.14</v>
+      </c>
+      <c r="U8">
+        <v>42921.25</v>
+      </c>
+      <c r="V8">
+        <v>294759.42</v>
+      </c>
+      <c r="W8">
+        <v>211525.39</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>4314.6498000000001</v>
+      </c>
+      <c r="AA8">
+        <v>193864.43</v>
+      </c>
+      <c r="AB8">
+        <v>191708.24</v>
+      </c>
+      <c r="AC8">
+        <v>385572.67</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>389887.32</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5874678.6399999997</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>156.6326</v>
+      </c>
+      <c r="H9" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I9" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J9">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K9" s="7">
+        <v>52200.379249999998</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>617.39575000000002</v>
+      </c>
+      <c r="O9">
+        <v>274.97000000000003</v>
+      </c>
+      <c r="P9">
+        <v>2784.23</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1623604</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>168604.14</v>
+      </c>
+      <c r="U9">
+        <v>855901</v>
+      </c>
+      <c r="V9">
+        <v>1427641.95</v>
+      </c>
+      <c r="W9">
+        <v>1024505.14</v>
+      </c>
+      <c r="X9">
+        <v>1192696.1499999999</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>32636.713100000001</v>
+      </c>
+      <c r="AA9">
+        <v>194832.49</v>
+      </c>
+      <c r="AB9">
+        <v>96717.95</v>
+      </c>
+      <c r="AC9">
+        <v>291550.44</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>324187.15000000002</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6232478.1600000001</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>156.6326</v>
+      </c>
+      <c r="H10" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I10" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J10">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K10" s="7">
+        <v>52257.521250000005</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>560.25374999999997</v>
+      </c>
+      <c r="O10">
+        <v>320.52999999999997</v>
+      </c>
+      <c r="P10">
+        <v>4375.8500000000004</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1629084</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>168604.14</v>
+      </c>
+      <c r="U10">
+        <v>1176523.29</v>
+      </c>
+      <c r="V10">
+        <v>1874427.21</v>
+      </c>
+      <c r="W10">
+        <v>1345127.43</v>
+      </c>
+      <c r="X10">
+        <v>1639478.09</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>43806.344599999997</v>
+      </c>
+      <c r="AA10">
+        <v>195490.08</v>
+      </c>
+      <c r="AB10">
+        <v>86345.42</v>
+      </c>
+      <c r="AC10">
+        <v>281835.5</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>325641.84000000003</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6562219.1100000003</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>156.6326</v>
+      </c>
+      <c r="H11" s="7">
+        <v>221721</v>
+      </c>
+      <c r="I11" s="7">
+        <v>211271</v>
+      </c>
+      <c r="J11">
+        <v>8.09E-2</v>
+      </c>
+      <c r="K11" s="7">
+        <v>52315.915999999997</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>501.85899999999998</v>
+      </c>
+      <c r="O11">
+        <v>323.48</v>
+      </c>
+      <c r="P11">
+        <v>5649.65</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>1630833</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>168604.14</v>
+      </c>
+      <c r="U11">
+        <v>1409841.33</v>
+      </c>
+      <c r="V11">
+        <v>2199554.5299999998</v>
+      </c>
+      <c r="W11">
+        <v>1578445.47</v>
+      </c>
+      <c r="X11">
+        <v>1964605.09</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>51934.527499999997</v>
+      </c>
+      <c r="AA11">
+        <v>195699.94</v>
+      </c>
+      <c r="AB11">
+        <v>83746.63</v>
+      </c>
+      <c r="AC11">
+        <v>279446.57</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>331381.09999999998</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A887E75F-7297-46F3-B28C-81BEAE0D863B}">
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>8</v>
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2">
+        <v>6.54</v>
+      </c>
+      <c r="C2">
+        <v>557370.56000000006</v>
+      </c>
+      <c r="D2">
+        <v>5657696.1299999999</v>
+      </c>
+      <c r="E2">
+        <v>6215066.6900000004</v>
+      </c>
+      <c r="F2">
+        <v>488.24770000000001</v>
+      </c>
+      <c r="G2">
+        <v>691139</v>
+      </c>
+      <c r="H2">
+        <v>658565</v>
+      </c>
+      <c r="I2">
+        <v>8.09E-2</v>
+      </c>
+      <c r="J2">
+        <v>141323.68099999998</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>23317.376499999998</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1259773</v>
+      </c>
+      <c r="Q2">
+        <v>1825067</v>
+      </c>
+      <c r="R2">
+        <v>0.22545449309861595</v>
+      </c>
+      <c r="S2">
+        <v>525564.84</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>732371.58</v>
+      </c>
+      <c r="V2">
+        <v>525564.84</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>8788.4590000000007</v>
+      </c>
+      <c r="Z2">
+        <v>151172.72</v>
+      </c>
+      <c r="AA2">
+        <v>185501.21</v>
+      </c>
+      <c r="AB2">
+        <v>336673.93</v>
+      </c>
+      <c r="AC2">
+        <v>419362.86</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>345462.39</v>
+      </c>
+      <c r="AF2">
+        <v>0.14799999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7893607-466D-4EF1-9DA9-CA73CB8976DC}">
+  <dimension ref="A1:AG12"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="7" customWidth="1"/>
+    <col min="8" max="9" width="11.875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="11" style="9"/>
+    <col min="11" max="16" width="11.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="32" width="11.125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20">
+        <v>6215066.6900000004</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>219008.09</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>200354.77</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>419362.86</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>419362.86</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="21">
+        <f>E2-E3</f>
+        <v>22.480000000447035</v>
+      </c>
+      <c r="E3" s="20">
         <v>6215044.21</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="G2" s="7">
+      <c r="H3" s="7">
         <v>12</v>
       </c>
-      <c r="H2" s="7">
+      <c r="I3" s="7">
         <v>11</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J3" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="J2">
+      <c r="K3" s="7">
         <v>2.8812500000000005</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="L3" s="7">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
         <v>1825056</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="R3" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
         <v>9.24</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
         <v>12.87</v>
       </c>
-      <c r="V2">
+      <c r="W3" s="3">
         <v>9.24</v>
       </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3">
         <v>0.1545</v>
       </c>
-      <c r="Z2">
+      <c r="AA3" s="3">
         <v>219006.71</v>
       </c>
-      <c r="AA2">
+      <c r="AB3" s="3">
         <v>200353.85</v>
       </c>
-      <c r="AB2">
+      <c r="AC3" s="3">
         <v>419360.56</v>
       </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+      <c r="AD3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3">
         <v>419360.71</v>
       </c>
-      <c r="AF2">
+      <c r="AG3">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="4" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="21">
+        <f t="shared" ref="D4:D12" si="0">E3-E4</f>
+        <v>557208.62999999989</v>
+      </c>
+      <c r="E4" s="20">
         <v>5657835.5800000001</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
         <v>496.89440000000002</v>
       </c>
-      <c r="G3" s="7">
+      <c r="H4" s="7">
         <v>703378</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I4" s="7">
         <v>670227</v>
       </c>
-      <c r="I3" s="9">
+      <c r="J4" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J3">
+      <c r="K4" s="7">
         <v>142695.122</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
+      <c r="L4" s="7">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
         <v>24861.667750000001</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
+      <c r="N4" s="7">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
         <v>1254287</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="R4" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
         <v>534872.34</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
         <v>745341.54</v>
       </c>
-      <c r="V3">
+      <c r="W4" s="3">
         <v>534872.34</v>
       </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
+      <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3">
         <v>8944.0985000000001</v>
       </c>
-      <c r="Z3">
+      <c r="AA4" s="3">
         <v>150514.44</v>
       </c>
-      <c r="AA3">
+      <c r="AB4" s="3">
         <v>185370.56</v>
       </c>
-      <c r="AB3">
+      <c r="AC4" s="3">
         <v>335885</v>
       </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3">
         <v>344829.1</v>
       </c>
-      <c r="AF3">
+      <c r="AG4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="5" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
         <v>15</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>-220382.11000000034</v>
+      </c>
+      <c r="E5" s="20">
         <v>5878217.6900000004</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
         <v>885.46529999999996</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H5" s="7">
         <v>1253420</v>
       </c>
-      <c r="H4" s="7">
+      <c r="I5" s="7">
         <v>1194344</v>
       </c>
-      <c r="I4" s="9">
+      <c r="J5" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J4">
+      <c r="K5" s="7">
         <v>178864.81475000002</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
         <v>119721.23849999999</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
         <v>1109608</v>
       </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="R5" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
         <v>953142.08</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="U5" s="3">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
         <v>1328198.01</v>
       </c>
-      <c r="V4">
+      <c r="W5" s="3">
         <v>953142.08</v>
       </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3">
         <v>15938.376099999999</v>
       </c>
-      <c r="Z4">
+      <c r="AA5" s="3">
         <v>133152.98000000001</v>
       </c>
-      <c r="AA4">
+      <c r="AB5" s="3">
         <v>181725.32</v>
       </c>
-      <c r="AB4">
+      <c r="AC5" s="3">
         <v>314878.3</v>
       </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
+      <c r="AD5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3">
         <v>330816.68</v>
       </c>
-      <c r="AF4">
+      <c r="AG5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="6" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <f t="shared" si="0"/>
+        <v>-324770.93999999948</v>
+      </c>
+      <c r="E6" s="20">
         <v>6202988.6299999999</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
         <v>1218.0920000000001</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H6" s="7">
         <v>1724269</v>
       </c>
-      <c r="H5" s="7">
+      <c r="I6" s="7">
         <v>1643002</v>
       </c>
-      <c r="I5" s="9">
+      <c r="J6" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J5">
+      <c r="K6" s="7">
         <v>192439.98800000001</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
         <v>218310.4535</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
         <v>1055308</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="R6" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
         <v>1311191.6000000001</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
         <v>1827137.97</v>
       </c>
-      <c r="V5">
+      <c r="W6" s="3">
         <v>1311191.6000000001</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3">
         <v>21925.655599999998</v>
       </c>
-      <c r="Z5">
+      <c r="AA6" s="3">
         <v>126636.9</v>
       </c>
-      <c r="AA5">
+      <c r="AB6" s="3">
         <v>179443.74</v>
       </c>
-      <c r="AB5">
+      <c r="AC6" s="3">
         <v>306080.64000000001</v>
       </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3">
         <v>328006.3</v>
       </c>
-      <c r="AF5">
+      <c r="AG6">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="7" spans="1:33" s="10" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="10">
         <v>25</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6537818.3799999999</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1519.6361999999999</v>
-      </c>
-      <c r="G6" s="7">
-        <v>2151120</v>
-      </c>
-      <c r="H6" s="7">
-        <v>2049735</v>
-      </c>
-      <c r="I6" s="9">
+      <c r="C7" s="10">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22">
+        <f t="shared" si="0"/>
+        <v>-902349.66000000015</v>
+      </c>
+      <c r="E7" s="23">
+        <v>7105338.29</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1305.7005999999999</v>
+      </c>
+      <c r="H7" s="13">
+        <v>1848283</v>
+      </c>
+      <c r="I7" s="13">
+        <v>1761171</v>
+      </c>
+      <c r="J7" s="14">
         <v>8.09E-2</v>
       </c>
-      <c r="J6">
-        <v>200376.00024999998</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>312057.5895</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1023563</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>1635783.1</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2279454.36</v>
-      </c>
-      <c r="V6">
-        <v>1635783.1</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>27353.452399999998</v>
-      </c>
-      <c r="Z6">
-        <v>122827.61</v>
-      </c>
-      <c r="AA6">
-        <v>178003.95</v>
-      </c>
-      <c r="AB6">
-        <v>300831.56</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>328185.01</v>
-      </c>
-      <c r="AF6">
+      <c r="K7" s="13">
+        <v>190509.74275</v>
+      </c>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13">
+        <v>45374.025499999996</v>
+      </c>
+      <c r="N7" s="13">
+        <v>204409.00625000001</v>
+      </c>
+      <c r="O7" s="13">
+        <v>499.53</v>
+      </c>
+      <c r="P7" s="13">
+        <v>12375.06</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>325911</v>
+      </c>
+      <c r="R7" s="13">
+        <v>1825067</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11">
+        <v>1405496.23</v>
+      </c>
+      <c r="U7" s="11">
+        <v>2753184.73</v>
+      </c>
+      <c r="V7" s="11">
+        <v>5795097.6699999999</v>
+      </c>
+      <c r="W7" s="11">
+        <v>4158680.96</v>
+      </c>
+      <c r="X7" s="11">
+        <v>3836550.22</v>
+      </c>
+      <c r="Y7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="11">
+        <v>119416.2797</v>
+      </c>
+      <c r="AA7" s="11">
+        <v>39109.31</v>
+      </c>
+      <c r="AB7" s="11">
+        <v>29033.79</v>
+      </c>
+      <c r="AC7" s="11">
+        <v>68143.100000000006</v>
+      </c>
+      <c r="AD7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="11">
+        <v>187559.38</v>
+      </c>
+      <c r="AG7" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="8" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>890294.08000000007</v>
+      </c>
+      <c r="E8" s="20">
         <v>6215044.21</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
         <v>8.6E-3</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H8" s="7">
         <v>12</v>
       </c>
-      <c r="H7" s="7">
+      <c r="I8" s="7">
         <v>11</v>
       </c>
-      <c r="I7" s="9">
+      <c r="J8" s="9">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="J7">
+      <c r="K8" s="7">
         <v>2.8812500000000005</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
         <v>1825056</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="R8" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>9.24</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>12.87</v>
       </c>
-      <c r="V7">
+      <c r="W8" s="3">
         <v>9.24</v>
       </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
         <v>0.1545</v>
       </c>
-      <c r="Z7">
+      <c r="AA8" s="3">
         <v>219006.71</v>
       </c>
-      <c r="AA7">
+      <c r="AB8" s="3">
         <v>200353.85</v>
       </c>
-      <c r="AB7">
+      <c r="AC8" s="3">
         <v>419360.56</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
         <v>419360.71</v>
       </c>
-      <c r="AF7">
+      <c r="AG8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="9" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>557208.62999999989</v>
+      </c>
+      <c r="E9" s="20">
         <v>5657835.5800000001</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
         <v>496.89440000000002</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H9" s="7">
         <v>703378</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I9" s="7">
         <v>670227</v>
       </c>
-      <c r="I8" s="9">
+      <c r="J9" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J8">
+      <c r="K9" s="7">
         <v>142695.122</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
         <v>24861.667750000001</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
         <v>1254287</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="R9" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
         <v>534872.34</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>745341.54</v>
       </c>
-      <c r="V8">
+      <c r="W9" s="3">
         <v>534872.34</v>
       </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
         <v>8944.0985000000001</v>
       </c>
-      <c r="Z8">
+      <c r="AA9" s="3">
         <v>150514.44</v>
       </c>
-      <c r="AA8">
+      <c r="AB9" s="3">
         <v>185370.56</v>
       </c>
-      <c r="AB8">
+      <c r="AC9" s="3">
         <v>335885</v>
       </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
+      <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
         <v>344829.1</v>
       </c>
-      <c r="AF8">
+      <c r="AG9">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="10" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10">
         <v>15</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
+        <v>326704.61000000034</v>
+      </c>
+      <c r="E10" s="20">
         <v>5331130.97</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
         <v>1106.5083999999999</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H10" s="7">
         <v>1566317</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I10" s="7">
         <v>1492494</v>
       </c>
-      <c r="I9" s="9">
+      <c r="J10" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J9">
+      <c r="K10" s="7">
         <v>184991.43549999999</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
         <v>23595.942999999999</v>
       </c>
-      <c r="M9">
+      <c r="N10" s="7">
         <v>164536.16425000003</v>
       </c>
-      <c r="N9">
+      <c r="O10" s="7">
         <v>392.63</v>
       </c>
-      <c r="O9">
+      <c r="P10" s="7">
         <v>5392.67</v>
       </c>
-      <c r="P9">
+      <c r="Q10" s="7">
         <v>492931</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="R10" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>1191079.6100000001</v>
       </c>
-      <c r="T9">
+      <c r="U10" s="3">
         <v>1411217.21</v>
       </c>
-      <c r="U9">
+      <c r="V10" s="3">
         <v>3626285.51</v>
       </c>
-      <c r="V9">
+      <c r="W10" s="3">
         <v>2602296.8199999998</v>
       </c>
-      <c r="W9">
+      <c r="X10" s="3">
         <v>1966526.35</v>
       </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
+      <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>69080.224100000007</v>
       </c>
-      <c r="Z9">
+      <c r="AA10" s="3">
         <v>59151.72</v>
       </c>
-      <c r="AA9">
+      <c r="AB10" s="3">
         <v>49378.97</v>
       </c>
-      <c r="AB9">
+      <c r="AC10" s="3">
         <v>108530.69</v>
       </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
         <v>177610.91</v>
       </c>
-      <c r="AF9">
+      <c r="AG10">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="11" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11">
         <v>20</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>-906189.79</v>
+      </c>
+      <c r="E11" s="20">
         <v>6237320.7599999998</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
         <v>1214.8742</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H11" s="7">
         <v>1719714</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I11" s="7">
         <v>1638661</v>
       </c>
-      <c r="I10" s="9">
+      <c r="J11" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J10">
+      <c r="K11" s="7">
         <v>187808.23175000001</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
         <v>32937.380499999999</v>
       </c>
-      <c r="M10">
+      <c r="N11" s="7">
         <v>188919.74724999999</v>
       </c>
-      <c r="N10">
+      <c r="O11" s="7">
         <v>448.52</v>
       </c>
-      <c r="O10">
+      <c r="P11" s="7">
         <v>9128.5300000000007</v>
       </c>
-      <c r="P10">
+      <c r="Q11" s="7">
         <v>392897</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="R11" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
         <v>1307727.8500000001</v>
       </c>
-      <c r="T10">
+      <c r="U11" s="3">
         <v>2128323</v>
       </c>
-      <c r="U10">
+      <c r="V11" s="3">
         <v>4788116.8499999996</v>
       </c>
-      <c r="V10">
+      <c r="W11" s="3">
         <v>3436050.84</v>
       </c>
-      <c r="W10">
+      <c r="X11" s="3">
         <v>2965800.45</v>
       </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
+      <c r="Y11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3">
         <v>96012.875</v>
       </c>
-      <c r="Z10">
+      <c r="AA11" s="3">
         <v>47147.65</v>
       </c>
-      <c r="AA10">
+      <c r="AB11" s="3">
         <v>36796.92</v>
       </c>
-      <c r="AB10">
+      <c r="AC11" s="3">
         <v>83944.57</v>
       </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3">
         <v>179957.44</v>
       </c>
-      <c r="AF10">
+      <c r="AG11">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="12" spans="1:33" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12">
         <v>25</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21">
+        <f t="shared" si="0"/>
+        <v>-868017.53000000026</v>
+      </c>
+      <c r="E12" s="20">
         <v>7105338.29</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
         <v>1305.7005999999999</v>
       </c>
-      <c r="G11" s="7">
+      <c r="H12" s="7">
         <v>1848283</v>
       </c>
-      <c r="H11" s="7">
+      <c r="I12" s="7">
         <v>1761171</v>
       </c>
-      <c r="I11" s="9">
+      <c r="J12" s="9">
         <v>8.09E-2</v>
       </c>
-      <c r="J11">
+      <c r="K12" s="7">
         <v>190509.74275</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
         <v>45374.025499999996</v>
       </c>
-      <c r="M11">
+      <c r="N12" s="7">
         <v>204409.00625000001</v>
       </c>
-      <c r="N11">
+      <c r="O12" s="7">
         <v>499.53</v>
       </c>
-      <c r="O11">
+      <c r="P12" s="7">
         <v>12375.06</v>
       </c>
-      <c r="P11">
+      <c r="Q12" s="7">
         <v>325911</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="R12" s="7">
+        <v>1825067</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>1405496.23</v>
       </c>
-      <c r="T11">
+      <c r="U12" s="3">
         <v>2753184.73</v>
       </c>
-      <c r="U11">
+      <c r="V12" s="3">
         <v>5795097.6699999999</v>
       </c>
-      <c r="V11">
+      <c r="W12" s="3">
         <v>4158680.96</v>
       </c>
-      <c r="W11">
+      <c r="X12" s="3">
         <v>3836550.22</v>
       </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
         <v>119416.2797</v>
       </c>
-      <c r="Z11">
+      <c r="AA12" s="3">
         <v>39109.31</v>
       </c>
-      <c r="AA11">
+      <c r="AB12" s="3">
         <v>29033.79</v>
       </c>
-      <c r="AB11">
+      <c r="AC12" s="3">
         <v>68143.100000000006</v>
       </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
         <v>187559.38</v>
       </c>
-      <c r="AF11">
+      <c r="AG12">
         <v>0</v>
       </c>
     </row>
